--- a/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92535544415</v>
+        <v>46157.93108788018</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93108788018</v>
+        <v>46157.93364891398</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93364891398</v>
+        <v>46157.93665898468</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93665898468</v>
+        <v>46158.28191463597</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28191463597</v>
+        <v>46158.29710706523</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29710706523</v>
+        <v>46158.29785790054</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29785790054</v>
+        <v>46158.33352457811</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33352457811</v>
+        <v>46158.37208962281</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.6_Данные_таблицы/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37208962281</v>
+        <v>46158.37425551158</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
